--- a/价格数据初步调整_客户A.xlsx
+++ b/价格数据初步调整_客户A.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1134"/>
+  <dimension ref="A1:F1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25390,6 +25390,1458 @@
         <v>56.8</v>
       </c>
     </row>
+    <row r="1135">
+      <c r="A1135" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1145" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1146" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1147" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1148" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1149" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1150" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1151" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1152" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1153" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1154" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1155" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1156" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1157" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1158" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1159" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1160" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1161" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1162" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1163" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1164" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1165" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1166" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1167" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1168" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1169" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1170" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1171" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1172" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1173" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1174" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1175" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1176" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1177" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1178" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1179" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>51.07</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1180" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1181" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1182" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1183" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1184" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1185" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1186" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1187" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1188" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1189" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1190" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1191" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1192" t="n">
+        <v>43.58</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1193" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1194" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1195" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1196" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1197" t="n">
+        <v>50.58</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1198" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1199" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1200" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>55.38</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户A.xlsx
+++ b/价格数据初步调整_客户A.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1200"/>
+  <dimension ref="A1:F1272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26842,6 +26842,1590 @@
         <v>55.8</v>
       </c>
     </row>
+    <row r="1201">
+      <c r="A1201" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1201" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1202" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1203" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1204" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1205" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1206" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1207" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1208" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1209" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1210" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1211" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1212" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1213" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1214" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1215" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1216" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1217" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1218" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1219" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1220" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1221" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1224" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1225" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1226" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1227" t="n">
+        <v>50.59</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1228" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1229" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1230" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>56.27</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1231" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1232" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1233" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1234" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1235" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1236" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1237" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1238" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1239" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1240" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1241" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1242" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1243" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1244" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1245" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1246" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1247" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1248" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1249" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1250" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1251" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1252" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1253" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1254" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1255" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1256" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1257" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1258" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1259" t="n">
+        <v>41</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1260" t="n">
+        <v>55.98</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>55.98</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1261" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>58.57</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1262" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1263" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1264" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1265" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1266" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1267" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>59.41</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1268" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1269" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="D1269" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1270" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1271" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="D1271" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="E1271" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="F1271" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1272" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户A.xlsx
+++ b/价格数据初步调整_客户A.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1272"/>
+  <dimension ref="A1:F1518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28426,6 +28426,5418 @@
         <v>55.8</v>
       </c>
     </row>
+    <row r="1273">
+      <c r="A1273" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1273" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>59.02</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1274" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="D1274" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="E1274" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="F1274" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1275" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1276" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="F1281" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="D1282" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="F1282" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="D1283" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="F1283" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="D1284" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>55.32</v>
+      </c>
+      <c r="F1284" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>58.08</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="F1285" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="D1287" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="E1287" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="F1287" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="D1288" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="E1288" t="n">
+        <v>42.54</v>
+      </c>
+      <c r="F1288" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="D1289" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="E1289" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="F1289" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="D1290" t="n">
+        <v>55.69</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="F1290" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="D1291" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="F1291" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="D1292" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="F1292" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="D1293" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="F1293" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="D1294" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="F1294" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="D1295" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="F1295" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="D1296" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="E1296" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="F1296" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>58.47</v>
+      </c>
+      <c r="D1297" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="F1297" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1298" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="D1298" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="F1298" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1299" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="D1299" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="F1299" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1300" t="n">
+        <v>42.76</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1301" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1302" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1303" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1305" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>55.33</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>49.19</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>41.08</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>55.98</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>50</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>40.69</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>41</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="F1398" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="F1399" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="E1400" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="F1400" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F1401" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F1402" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F1403" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="F1404" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="F1405" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="F1406" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="F1407" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="F1408" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1411" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F1412" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="F1413" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="F1414" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="F1427" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="D1430" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1436" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1437" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1438" t="n">
+        <v>42.76</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1439" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1440" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1441" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1442" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1443" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="D1443" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="F1443" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1444" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="D1444" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="E1444" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="F1444" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1445" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="D1445" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="F1445" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1446" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="D1446" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="F1446" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1447" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1447" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1448" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="D1448" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="F1448" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1449" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1450" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1451" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1452" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1453" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1454" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1455" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="D1455" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1456" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1457" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1458" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1459" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1460" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1461" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1462" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1463" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1464" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1465" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1466" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1467" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1468" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1469" t="n">
+        <v>41</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1470" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1471" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1472" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1473" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1474" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1475" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1476" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1477" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>59.61</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1478" t="n">
+        <v>58.06</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1479" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1480" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1481" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1482" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1483" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1484" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1485" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1486" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1487" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1488" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>56</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1489" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1490" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1491" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1492" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1493" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1494" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1495" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1496" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1497" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1498" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1499" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1500" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>55.69</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1501" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1502" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>57.38</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1503" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1504" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1505" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>55.33</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1509" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1510" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>42.76</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1511" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="D1511" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1512" t="n">
+        <v>55.39</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1513" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1514" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1515" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="D1515" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1516" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1517" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1518" t="n">
+        <v>55.32</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户A.xlsx
+++ b/价格数据初步调整_客户A.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1518"/>
+  <dimension ref="A1:F1656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33838,6 +33838,3042 @@
         <v>55.6</v>
       </c>
     </row>
+    <row r="1519">
+      <c r="A1519" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1519" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1520" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1521" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="D1521" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1522" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="D1522" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1523" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="D1523" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1524" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1525" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="D1525" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1526" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="D1526" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1527" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="D1527" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1528" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1529" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1530" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>55.32</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1531" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1531" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1532" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="D1532" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1533" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="D1533" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1534" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="D1534" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="E1534" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="F1534" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1535" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="D1535" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1536" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="D1536" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>55.38</v>
+      </c>
+      <c r="F1536" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1537" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="D1537" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1537" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1538" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="D1538" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="E1538" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1539" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="D1539" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1540" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="D1540" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1541" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="D1541" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="E1541" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1542" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="D1542" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="E1542" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1543" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="D1543" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="E1543" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1544" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="D1544" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="F1544" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1545" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1546" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="F1546" t="n">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1547" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1548" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="D1548" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1549" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="D1549" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1550" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="D1550" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1551" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="D1551" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1552" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1553" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1554" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1555" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1556" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1557" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1558" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="D1558" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1559" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="D1559" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1560" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="D1560" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="F1560" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1561" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1562" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="D1562" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1563" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="D1563" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1564" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="D1564" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="F1564" t="n">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1565" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="D1565" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="E1565" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="F1565" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1566" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="D1566" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="E1566" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="F1566" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1567" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1567" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1568" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="D1568" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="E1568" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1569" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="D1569" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="F1569" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1570" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1570" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1571" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D1571" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1572" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="D1572" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1573" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1573" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1574" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="D1574" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1575" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D1575" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1576" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="D1576" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1577" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="D1577" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1578" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1579" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1580" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1581" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1582" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1583" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1584" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1585" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1586" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="D1586" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1587" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1588" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="D1588" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1589" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="D1589" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1590" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="D1590" t="n">
+        <v>55.39</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1591" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="D1591" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1592" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="D1592" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1593" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="D1593" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1594" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="D1594" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1595" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="D1595" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1596" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="D1596" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1597" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="D1597" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1598" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="D1598" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F1598" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1599" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="D1599" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1600" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="D1600" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1601" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="D1601" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1602" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="D1602" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1603" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="D1603" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1604" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="D1604" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="F1604" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1605" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D1605" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="F1605" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1606" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="D1606" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="F1606" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1607" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="D1607" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1608" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="D1608" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1609" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="D1609" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1610" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="D1610" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="E1610" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1611" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="D1611" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1612" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="D1612" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1613" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="D1613" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1614" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="D1614" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1615" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="D1615" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1616" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="D1616" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1617" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="D1617" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1618" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="D1618" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1619" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="D1619" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1620" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="D1620" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1621" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="D1621" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1622" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="D1622" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1623" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="D1623" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="F1623" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1624" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="D1624" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1625" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="D1625" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1626" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="D1626" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1627" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="D1627" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1628" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D1628" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1629" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="D1629" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1630" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="D1630" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1631" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="D1631" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1632" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="D1632" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="F1632" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1633" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1633" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1634" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="D1634" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1635" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D1635" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1636" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="D1636" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="D1637" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="D1638" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="F1638" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1639" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="F1639" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="D1640" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="D1641" t="n">
+        <v>48.36</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="D1642" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="D1643" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="D1644" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1645" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="D1646" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="D1647" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="D1648" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="D1649" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="F1649" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="D1650" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="D1653" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="D1654" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1655" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1656" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="D1656" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="F1656" t="n">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户A.xlsx
+++ b/价格数据初步调整_客户A.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1656"/>
+  <dimension ref="A1:F1866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36874,6 +36874,4626 @@
         <v>55</v>
       </c>
     </row>
+    <row r="1657">
+      <c r="A1657" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1657" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="D1657" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="F1657" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1658" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="D1658" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1659" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D1659" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1660" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="D1660" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="F1660" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1661" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="D1661" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F1661" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="D1662" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="F1662" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1663" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="D1663" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="F1663" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1664" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="D1664" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="F1664" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="D1665" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="E1665" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="F1665" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="D1666" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="F1666" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="D1667" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="D1669" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="F1669" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="D1670" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="F1670" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="D1671" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F1671" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D1673" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="D1674" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E1674" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="F1674" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="D1675" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="D1676" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="D1677" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E1677" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1678" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="D1678" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1679" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="D1679" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1680" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1681" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="D1681" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1682" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="D1682" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1683" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="D1683" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="D1684" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="E1684" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F1684" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="D1685" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="D1686" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1687" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="D1687" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="F1687" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1688" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D1688" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1689" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="D1689" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="E1689" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="D1690" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1691" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="D1691" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1692" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="D1692" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1693" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="D1693" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1694" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="D1694" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1695" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="D1695" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="E1695" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F1695" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="D1696" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="D1697" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>55.33</v>
+      </c>
+      <c r="D1698" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1699" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1699" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1699" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="F1699" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1700" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="D1700" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1701" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="D1701" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="F1701" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1702" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="D1702" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="F1702" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1703" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="D1703" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1704" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="D1704" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="F1704" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1705" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1705" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="F1705" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1706" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="D1706" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="E1706" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="F1706" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1707" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="D1707" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1708" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="D1708" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="E1708" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1709" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="D1709" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="E1709" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="F1709" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1710" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="D1710" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1711" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1711" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1712" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="D1712" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1713" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="D1713" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="F1713" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1714" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="D1714" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1715" t="n">
+        <v>41</v>
+      </c>
+      <c r="D1715" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="F1715" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1716" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="D1716" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="F1716" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1717" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="D1717" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1718" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="D1718" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1719" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="D1719" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1720" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="D1720" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1721" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="D1721" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E1721" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1721" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1722" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="D1722" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="E1722" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="F1722" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1723" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="D1723" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1724" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="D1724" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1725" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="D1725" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1726" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="D1726" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1727" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="D1727" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1728" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D1728" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="F1728" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1729" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1730" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1731" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="D1731" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1732" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="D1732" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1733" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="D1733" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1734" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1735" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="D1735" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1736" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="D1736" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="F1736" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1737" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1738" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1739" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1740" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1741" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1742" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1743" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1744" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="D1744" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1745" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1746" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D1746" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1747" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1748" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1749" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1750" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1751" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1752" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1753" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1754" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F1754" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1755" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1756" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1757" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1758" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1759" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1760" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1761" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="D1761" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1762" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="D1762" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1763" t="n">
+        <v>41</v>
+      </c>
+      <c r="D1763" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1764" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1765" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1766" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="D1766" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="F1766" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1767" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="D1767" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="F1767" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1768" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="D1768" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1769" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="D1769" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1770" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="D1770" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1771" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1771" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1772" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1773" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="D1773" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="F1773" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1774" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="D1774" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="E1774" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F1774" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1775" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="D1775" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1776" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="D1776" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1777" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1777" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="F1777" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1778" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="D1778" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1779" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="D1779" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="E1779" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="F1779" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1780" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="D1780" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="F1780" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1781" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="D1781" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="F1781" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1782" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="D1782" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="E1782" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="F1782" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1783" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1783" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E1783" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="F1783" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1784" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="D1784" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="E1784" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="F1784" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1785" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="D1785" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="E1785" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="F1785" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1786" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="D1786" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="E1786" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F1786" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1787" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="D1787" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E1787" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="F1787" t="n">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1788" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="D1788" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="E1788" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="F1788" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1789" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="D1789" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="E1789" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="F1789" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1790" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="D1790" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="E1790" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="F1790" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1791" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="D1791" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="E1791" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="F1791" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1792" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="D1792" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E1792" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="F1792" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1793" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="D1793" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="E1793" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="F1793" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1794" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="D1794" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="E1794" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="F1794" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1795" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="D1795" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="E1795" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="F1795" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1796" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="D1796" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="E1796" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="F1796" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1797" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="D1797" t="n">
+        <v>47.69</v>
+      </c>
+      <c r="E1797" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="F1797" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1798" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="D1798" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="E1798" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="F1798" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1799" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="D1799" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="E1799" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="F1799" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1800" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="D1800" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="E1800" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="F1800" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1801" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="D1801" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="E1801" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="F1801" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1802" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="D1802" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="E1802" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="F1802" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1803" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="D1803" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E1803" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="F1803" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1804" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="D1804" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="E1804" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="F1804" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1805" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="D1805" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="E1805" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="F1805" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1806" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="D1806" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="E1806" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="F1806" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1807" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="D1807" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="E1807" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="F1807" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1808" t="n">
+        <v>56.27</v>
+      </c>
+      <c r="D1808" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="E1808" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F1808" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1809" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="D1809" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="E1809" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="F1809" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1810" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="D1810" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="E1810" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="F1810" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1811" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="D1811" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="E1811" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="F1811" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1812" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="D1812" t="n">
+        <v>55</v>
+      </c>
+      <c r="E1812" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="F1812" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1813" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="D1813" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="E1813" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="F1813" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1814" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="D1814" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="E1814" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="F1814" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1815" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="D1815" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="E1815" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="F1815" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1816" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="D1816" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="F1816" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1817" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="D1817" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="F1817" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1818" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="D1818" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="E1818" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="F1818" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1819" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="D1819" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="E1819" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="F1819" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1820" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="D1820" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="E1820" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="F1820" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1821" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="D1821" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="E1821" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F1821" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1822" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="D1822" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="E1822" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F1822" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1823" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="D1823" t="n">
+        <v>40.69</v>
+      </c>
+      <c r="E1823" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="F1823" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1824" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="D1824" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="E1824" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="F1824" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1825" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="D1825" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1825" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="F1825" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1826" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="D1826" t="n">
+        <v>57.38</v>
+      </c>
+      <c r="E1826" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="F1826" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1827" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="D1827" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="E1827" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="F1827" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1828" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1829" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="F1829" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1830" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1831" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="D1831" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="F1831" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1832" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1833" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1834" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1835" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1836" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1837" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1838" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1839" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1840" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1841" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1842" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1843" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1844" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1845" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1846" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1847" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1848" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>54.13</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1849" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="D1849" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1850" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="D1850" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1851" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="D1851" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="E1851" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="F1851" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1852" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="D1852" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="E1852" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="F1852" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1853" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="D1853" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="E1853" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="F1853" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1854" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="D1854" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="E1854" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="F1854" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1855" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="D1855" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="E1855" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="F1855" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1856" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="D1856" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="E1856" t="n">
+        <v>56.37</v>
+      </c>
+      <c r="F1856" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1857" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="D1857" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="E1857" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="F1857" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1858" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="D1858" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="E1858" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="F1858" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1859" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="D1859" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="E1859" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="F1859" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1860" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="D1860" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="E1860" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="F1860" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1861" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="D1861" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="E1861" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="F1861" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1862" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="D1862" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="E1862" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="F1862" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1863" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="D1863" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="E1863" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F1863" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1864" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="D1864" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="E1864" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="F1864" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1865" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="D1865" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="E1865" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F1865" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1866" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="D1866" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="E1866" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="F1866" t="n">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户A.xlsx
+++ b/价格数据初步调整_客户A.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1866"/>
+  <dimension ref="A1:F2094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39986,16 +39986,16 @@
         </is>
       </c>
       <c r="C1798" t="n">
-        <v>41.27</v>
+        <v>41.68</v>
       </c>
       <c r="D1798" t="n">
-        <v>41.52</v>
+        <v>41.72</v>
       </c>
       <c r="E1798" t="n">
-        <v>41.22</v>
+        <v>41.62</v>
       </c>
       <c r="F1798" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="1799">
@@ -40118,16 +40118,16 @@
         </is>
       </c>
       <c r="C1804" t="n">
-        <v>41.22</v>
+        <v>41.79</v>
       </c>
       <c r="D1804" t="n">
-        <v>41.79</v>
+        <v>42.09</v>
       </c>
       <c r="E1804" t="n">
-        <v>41.05</v>
+        <v>41.62</v>
       </c>
       <c r="F1804" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1805">
@@ -40250,16 +40250,16 @@
         </is>
       </c>
       <c r="C1810" t="n">
-        <v>41.61</v>
+        <v>41.87</v>
       </c>
       <c r="D1810" t="n">
-        <v>41.79</v>
+        <v>42.17</v>
       </c>
       <c r="E1810" t="n">
-        <v>41.25</v>
+        <v>41.71</v>
       </c>
       <c r="F1810" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="1811">
@@ -40382,16 +40382,16 @@
         </is>
       </c>
       <c r="C1816" t="n">
-        <v>41.24</v>
+        <v>41.64</v>
       </c>
       <c r="D1816" t="n">
-        <v>41.78</v>
+        <v>42.18</v>
       </c>
       <c r="E1816" t="n">
-        <v>41.13</v>
+        <v>41.53</v>
       </c>
       <c r="F1816" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="1817">
@@ -40514,16 +40514,16 @@
         </is>
       </c>
       <c r="C1822" t="n">
-        <v>41.57</v>
+        <v>41.83</v>
       </c>
       <c r="D1822" t="n">
-        <v>41.88</v>
+        <v>42.02</v>
       </c>
       <c r="E1822" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="F1822" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1823">
@@ -40646,16 +40646,16 @@
         </is>
       </c>
       <c r="C1828" t="n">
-        <v>41.28</v>
+        <v>41.47</v>
       </c>
       <c r="D1828" t="n">
-        <v>41.67</v>
+        <v>41.87</v>
       </c>
       <c r="E1828" t="n">
-        <v>41.19</v>
+        <v>41.39</v>
       </c>
       <c r="F1828" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1829">
@@ -40778,16 +40778,16 @@
         </is>
       </c>
       <c r="C1834" t="n">
-        <v>41.86</v>
+        <v>42.07</v>
       </c>
       <c r="D1834" t="n">
-        <v>42.04</v>
+        <v>42.25</v>
       </c>
       <c r="E1834" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="F1834" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1835">
@@ -40910,16 +40910,16 @@
         </is>
       </c>
       <c r="C1840" t="n">
-        <v>41.61</v>
+        <v>41.72</v>
       </c>
       <c r="D1840" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="F1840" t="n">
         <v>41.7</v>
-      </c>
-      <c r="E1840" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="F1840" t="n">
-        <v>41.6</v>
       </c>
     </row>
     <row r="1841">
@@ -41042,16 +41042,16 @@
         </is>
       </c>
       <c r="C1846" t="n">
-        <v>41.28</v>
+        <v>41.38</v>
       </c>
       <c r="D1846" t="n">
-        <v>41.71</v>
+        <v>41.81</v>
       </c>
       <c r="E1846" t="n">
-        <v>41.09</v>
+        <v>41.19</v>
       </c>
       <c r="F1846" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="1847">
@@ -41174,16 +41174,16 @@
         </is>
       </c>
       <c r="C1852" t="n">
-        <v>41.45</v>
+        <v>41.55</v>
       </c>
       <c r="D1852" t="n">
-        <v>41.76</v>
+        <v>41.86</v>
       </c>
       <c r="E1852" t="n">
-        <v>41.31</v>
+        <v>41.41</v>
       </c>
       <c r="F1852" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="1853">
@@ -41306,16 +41306,16 @@
         </is>
       </c>
       <c r="C1858" t="n">
-        <v>41.49</v>
+        <v>41.59</v>
       </c>
       <c r="D1858" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="E1858" t="n">
-        <v>41.29</v>
+        <v>41.39</v>
       </c>
       <c r="F1858" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="1859">
@@ -41372,16 +41372,16 @@
         </is>
       </c>
       <c r="C1861" t="n">
-        <v>59.23</v>
+        <v>59.01</v>
       </c>
       <c r="D1861" t="n">
-        <v>59.51</v>
+        <v>59.63</v>
       </c>
       <c r="E1861" t="n">
-        <v>58.34</v>
+        <v>58.77</v>
       </c>
       <c r="F1861" t="n">
-        <v>58.7</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="1862">
@@ -41394,16 +41394,16 @@
         </is>
       </c>
       <c r="C1862" t="n">
-        <v>57.35</v>
+        <v>57.4</v>
       </c>
       <c r="D1862" t="n">
-        <v>57.57</v>
+        <v>58.13</v>
       </c>
       <c r="E1862" t="n">
-        <v>56.72</v>
+        <v>57.34</v>
       </c>
       <c r="F1862" t="n">
-        <v>56.8</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="1863">
@@ -41416,16 +41416,16 @@
         </is>
       </c>
       <c r="C1863" t="n">
-        <v>48.48</v>
+        <v>50.87</v>
       </c>
       <c r="D1863" t="n">
-        <v>48.65</v>
+        <v>51.16</v>
       </c>
       <c r="E1863" t="n">
-        <v>48.3</v>
+        <v>50.68</v>
       </c>
       <c r="F1863" t="n">
-        <v>48.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1864">
@@ -41438,16 +41438,16 @@
         </is>
       </c>
       <c r="C1864" t="n">
-        <v>41.39</v>
+        <v>42.33</v>
       </c>
       <c r="D1864" t="n">
-        <v>41.76</v>
+        <v>42.56</v>
       </c>
       <c r="E1864" t="n">
-        <v>41.33</v>
+        <v>42.26</v>
       </c>
       <c r="F1864" t="n">
-        <v>41.6</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="1865">
@@ -41460,16 +41460,16 @@
         </is>
       </c>
       <c r="C1865" t="n">
-        <v>40.31</v>
+        <v>41.64</v>
       </c>
       <c r="D1865" t="n">
-        <v>40.68</v>
+        <v>42.09</v>
       </c>
       <c r="E1865" t="n">
-        <v>40.28</v>
+        <v>41.61</v>
       </c>
       <c r="F1865" t="n">
-        <v>40.4</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1866">
@@ -41482,16 +41482,5032 @@
         </is>
       </c>
       <c r="C1866" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="D1866" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="E1866" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="F1866" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1867" t="n">
+        <v>59.71</v>
+      </c>
+      <c r="D1867" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="E1867" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="F1867" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1868" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="D1868" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="E1868" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="F1868" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1869" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="D1869" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E1869" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="F1869" t="n">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1870" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="D1870" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="E1870" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="F1870" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1871" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="D1871" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="E1871" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="F1871" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1872" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="D1872" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="E1872" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="F1872" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1873" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="D1873" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="E1873" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="F1873" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1874" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="D1874" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E1874" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="F1874" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1875" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="D1875" t="n">
+        <v>51.61</v>
+      </c>
+      <c r="E1875" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="F1875" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1876" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="D1876" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="E1876" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="F1876" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1877" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="D1877" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="E1877" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="F1877" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1878" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="D1878" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="E1878" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="F1878" t="n">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1879" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="D1879" t="n">
+        <v>60.89</v>
+      </c>
+      <c r="E1879" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="F1879" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1880" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="D1880" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="E1880" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="F1880" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1881" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="D1881" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="E1881" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="F1881" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1882" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="D1882" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="E1882" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="F1882" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1883" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="D1883" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="E1883" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F1883" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1884" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="D1884" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E1884" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="F1884" t="n">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1885" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="D1885" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="E1885" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="F1885" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1886" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="D1886" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="E1886" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="F1886" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1887" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="D1887" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="E1887" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="F1887" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1888" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="D1888" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="E1888" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="F1888" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1889" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="D1889" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E1889" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="F1889" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1890" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="D1890" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="E1890" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="F1890" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1891" t="n">
+        <v>60.83</v>
+      </c>
+      <c r="D1891" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E1891" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="F1891" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1892" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="D1892" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E1892" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="F1892" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1893" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="D1893" t="n">
+        <v>52.32</v>
+      </c>
+      <c r="E1893" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="F1893" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1894" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="D1894" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="E1894" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="F1894" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1895" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="D1895" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="E1895" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="F1895" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1896" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="D1896" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="E1896" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="F1896" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1897" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="D1897" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="E1897" t="n">
+        <v>60.45</v>
+      </c>
+      <c r="F1897" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1898" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="D1898" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="E1898" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="F1898" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1899" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="D1899" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="E1899" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="F1899" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1900" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="D1900" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="E1900" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="F1900" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1901" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="D1901" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="E1901" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="F1901" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1902" t="n">
+        <v>56</v>
+      </c>
+      <c r="D1902" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="E1902" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="F1902" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1903" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="D1903" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="E1903" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="F1903" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1904" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="D1904" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="E1904" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="F1904" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1905" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="D1905" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="E1905" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="F1905" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1906" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="D1906" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="E1906" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="F1906" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1907" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="D1907" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="E1907" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="F1907" t="n">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1908" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="D1908" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="E1908" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F1908" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1909" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="D1909" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="E1909" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="F1909" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1910" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="D1910" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="E1910" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="F1910" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1911" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D1911" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="E1911" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="F1911" t="n">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1912" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="D1912" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="E1912" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="F1912" t="n">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1913" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D1913" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="E1913" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="F1913" t="n">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1914" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D1914" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="E1914" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="F1914" t="n">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1915" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="D1915" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="E1915" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="F1915" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1916" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="D1916" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="E1916" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="F1916" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1917" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="D1917" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="E1917" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="F1917" t="n">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1918" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="D1918" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="E1918" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="F1918" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1919" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="D1919" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="E1919" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="F1919" t="n">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1920" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="D1920" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="E1920" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="F1920" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1921" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="D1921" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="E1921" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="F1921" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1922" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="D1922" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="E1922" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="F1922" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1923" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="D1923" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="E1923" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="F1923" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1924" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="D1924" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="E1924" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="F1924" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1925" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="D1925" t="n">
+        <v>45.02</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="F1925" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1926" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="D1926" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="F1926" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1927" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1928" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1929" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1930" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="F1930" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1931" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1932" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1933" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="D1933" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="E1933" t="n">
+        <v>62.43</v>
+      </c>
+      <c r="F1933" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1934" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>61.26</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>60.98</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1935" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1936" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="F1936" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1937" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1938" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="D1938" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E1938" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="F1938" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1939" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="D1939" t="n">
+        <v>62.91</v>
+      </c>
+      <c r="E1939" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="F1939" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1940" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="D1940" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="E1940" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="F1940" t="n">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1941" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="D1941" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="E1941" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="F1941" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1942" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="D1942" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E1942" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="F1942" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1943" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="D1943" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="E1943" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="F1943" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1944" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="D1944" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="E1944" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="F1944" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1945" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="D1945" t="n">
+        <v>62.77</v>
+      </c>
+      <c r="E1945" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="F1945" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1946" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="D1946" t="n">
+        <v>61.49</v>
+      </c>
+      <c r="E1946" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="F1946" t="n">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1947" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="D1947" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="E1947" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="F1947" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1948" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="D1948" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="E1948" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="F1948" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1949" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="D1949" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="E1949" t="n">
+        <v>45.61</v>
+      </c>
+      <c r="F1949" t="n">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1950" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="D1950" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="E1950" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="F1950" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1951" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="D1951" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="E1951" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="F1951" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1952" t="n">
+        <v>61.26</v>
+      </c>
+      <c r="D1952" t="n">
+        <v>61.31</v>
+      </c>
+      <c r="E1952" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="F1952" t="n">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1953" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="D1953" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="E1953" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="F1953" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1954" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="D1954" t="n">
+        <v>47</v>
+      </c>
+      <c r="E1954" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="F1954" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1955" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="D1955" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="E1955" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="F1955" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1956" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="D1956" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="E1956" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="F1956" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1957" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D1957" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="E1957" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="F1957" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1958" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="D1958" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="E1958" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="F1958" t="n">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1959" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="D1959" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="E1959" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="F1959" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1960" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="D1960" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="E1960" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="F1960" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1961" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="D1961" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="E1961" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="F1961" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1962" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="D1962" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="E1962" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="F1962" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1963" t="n">
+        <v>62.61</v>
+      </c>
+      <c r="D1963" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="E1963" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="F1963" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1964" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="D1964" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E1964" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="F1964" t="n">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1965" t="n">
+        <v>54.09</v>
+      </c>
+      <c r="D1965" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="E1965" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="F1965" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1966" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="D1966" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="E1966" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="F1966" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1967" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="D1967" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="E1967" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="F1967" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1968" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="D1968" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="E1968" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="F1968" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1969" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="D1969" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="E1969" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="F1969" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1970" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="D1970" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="E1970" t="n">
+        <v>60.69</v>
+      </c>
+      <c r="F1970" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1971" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="D1971" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E1971" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F1971" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1972" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="D1972" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="E1972" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="F1972" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1973" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="D1973" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="E1973" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="F1973" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1974" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="D1974" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="E1974" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="F1974" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1975" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="D1975" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="E1975" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="F1975" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1976" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="D1976" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="E1976" t="n">
+        <v>60.41</v>
+      </c>
+      <c r="F1976" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1977" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="D1977" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="E1977" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="F1977" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1978" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="D1978" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="E1978" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="F1978" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1979" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="D1979" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="E1979" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="F1979" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1980" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="D1980" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="E1980" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="F1980" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1981" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="D1981" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="E1981" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="F1981" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1982" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="D1982" t="n">
+        <v>60.93</v>
+      </c>
+      <c r="E1982" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="F1982" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1983" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="D1983" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="E1983" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F1983" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1984" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="D1984" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="E1984" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="F1984" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1985" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="D1985" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="E1985" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F1985" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1986" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="D1986" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="E1986" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="F1986" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1987" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="D1987" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="E1987" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="F1987" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1988" t="n">
+        <v>60.36</v>
+      </c>
+      <c r="D1988" t="n">
+        <v>61.17</v>
+      </c>
+      <c r="E1988" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="F1988" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1989" t="n">
+        <v>54</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="E1989" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="F1989" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1990" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="D1990" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E1990" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="F1990" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1991" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="D1991" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="E1991" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1992" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="E1992" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1993" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="E1993" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="F1993" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C1994" t="n">
+        <v>61.39</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="E1994" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="F1994" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C1995" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="D1995" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="E1995" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="F1995" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C1996" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="E1996" t="n">
+        <v>48.19</v>
+      </c>
+      <c r="F1996" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C1997" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="E1997" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C1998" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="E1998" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="F1998" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C1999" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="E1999" t="n">
+        <v>62.31</v>
+      </c>
+      <c r="F1999" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2000" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="E2000" t="n">
+        <v>60.36</v>
+      </c>
+      <c r="F2000" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2001" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="F2001" t="n">
         <v>53.7</v>
       </c>
-      <c r="D1866" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="E1866" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="F1866" t="n">
+    </row>
+    <row r="2002">
+      <c r="A2002" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2002" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="F2002" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2003" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="E2003" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="F2003" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2004" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="E2004" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F2004" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2005" t="n">
+        <v>62.82</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="E2005" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="F2005" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2006" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>61.42</v>
+      </c>
+      <c r="E2006" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="F2006" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2007" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2008" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2009" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="E2009" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="F2009" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2010" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2011" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>63.11</v>
+      </c>
+      <c r="E2011" t="n">
+        <v>61.96</v>
+      </c>
+      <c r="F2011" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2012" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="E2012" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2013" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="F2013" t="n">
         <v>54</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2014" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E2014" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2015" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2016" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="E2016" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2017" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2018" t="n">
+        <v>60.98</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>60.89</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2019" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="E2019" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2020" t="n">
+        <v>48.39</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2021" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="E2021" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2022" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="E2022" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="F2022" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2023" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>63.18</v>
+      </c>
+      <c r="E2023" t="n">
+        <v>62.61</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2024" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="E2024" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2025" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="E2025" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2026" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="E2026" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="F2026" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2027" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="E2027" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2028" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="E2028" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2029" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="E2029" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2030" t="n">
+        <v>60.83</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="E2030" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2031" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="E2031" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="F2031" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2032" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="E2032" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2033" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="E2033" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="F2033" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2034" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E2034" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2035" t="n">
+        <v>62.61</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="E2035" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="F2035" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2036" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="E2036" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="F2036" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2037" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="E2037" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="F2037" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2038" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="E2038" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="F2038" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2039" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="E2039" t="n">
+        <v>46.27</v>
+      </c>
+      <c r="F2039" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2040" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="E2040" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="F2040" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2041" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="E2041" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="F2041" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2042" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="E2042" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="F2042" t="n">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2043" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="E2043" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="F2043" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2044" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="E2044" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="F2044" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2045" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="E2045" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="F2045" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2046" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="E2046" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="F2046" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2047" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="E2047" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="F2047" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2048" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="E2048" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="F2048" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2049" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="E2049" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="F2049" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2050" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="E2050" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="F2050" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2051" t="n">
+        <v>46.34</v>
+      </c>
+      <c r="D2051" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="E2051" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="F2051" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2052" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="E2052" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F2052" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2053" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="E2053" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="F2053" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2054" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="E2054" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F2054" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2055" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="E2055" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="F2055" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2056" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="E2056" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="F2056" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2057" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="E2057" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2058" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="D2058" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="E2058" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="F2058" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2059" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2060" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="E2060" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>61.7</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2061" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2062" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="E2062" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2063" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2064" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="E2064" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2065" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="E2065" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="F2065" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2066" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>61.7</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2067" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2068" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2069" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2070" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2071" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2072" t="n">
+        <v>61.96</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2073" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2074" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2075" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2076" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2077" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2078" t="n">
+        <v>62.17</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2079" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2080" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2081" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2082" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2083" t="n">
+        <v>62.22</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2084" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>61.29</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2085" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2086" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2087" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2088" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2089" t="n">
+        <v>63</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2090" t="n">
+        <v>62.39</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>62.23</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2091" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2092" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2093" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>47.03</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2094" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>58.3</v>
       </c>
     </row>
   </sheetData>

--- a/价格数据初步调整_客户A.xlsx
+++ b/价格数据初步调整_客户A.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2094"/>
+  <dimension ref="A1:F2364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46510,6 +46510,5946 @@
         <v>58.3</v>
       </c>
     </row>
+    <row r="2095">
+      <c r="A2095" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2095" t="n">
+        <v>63.22</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2096" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2097" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2098" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2099" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2100" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2101" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2102" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2103" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2104" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2105" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2106" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2107" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2108" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>62.47</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2109" t="n">
+        <v>57</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2110" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2111" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2112" t="n">
+        <v>59</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2113" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>63.34</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2114" t="n">
+        <v>63</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>62.91</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2115" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2116" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2117" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2118" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>59.58</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>59.16</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2119" t="n">
+        <v>64.22</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2120" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2121" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2122" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2123" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2124" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2125" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2126" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2127" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2128" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="E2128" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="F2128" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2129" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2130" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="E2130" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="F2130" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2131" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="E2131" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="F2131" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2132" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="E2132" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2133" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="E2133" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="F2133" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2134" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="E2134" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="F2134" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2135" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="E2135" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="F2135" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2136" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="E2136" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="F2136" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2137" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="E2137" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="F2137" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2138" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="E2138" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="F2138" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2139" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="E2139" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2140" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="D2140" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E2140" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="F2140" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2141" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="D2141" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="E2141" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="F2141" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2142" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="D2142" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="E2142" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="F2142" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2143" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="D2143" t="n">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="E2143" t="n">
+        <v>65.14</v>
+      </c>
+      <c r="F2143" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2144" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="E2144" t="n">
+        <v>62.81</v>
+      </c>
+      <c r="F2144" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2145" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D2145" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="E2145" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="F2145" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2146" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="E2146" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F2146" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2147" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="D2147" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="E2147" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="F2147" t="n">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2148" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="D2148" t="n">
+        <v>59.54</v>
+      </c>
+      <c r="E2148" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="F2148" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2149" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="D2149" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="E2149" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="F2149" t="n">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2150" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="D2150" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="E2150" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="F2150" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2151" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="D2151" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="E2151" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="F2151" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2152" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="D2152" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="E2152" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="F2152" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2153" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="D2153" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="E2153" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="F2153" t="n">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2154" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="D2154" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="E2154" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="F2154" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2155" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="D2155" t="n">
+        <v>65.78</v>
+      </c>
+      <c r="E2155" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="F2155" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2156" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="D2156" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="E2156" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="F2156" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2157" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="D2157" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E2157" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="F2157" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2158" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="D2158" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="E2158" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="F2158" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2159" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="D2159" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="E2159" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="F2159" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2160" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="D2160" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="E2160" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="F2160" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2161" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="D2161" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="E2161" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F2161" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2162" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="D2162" t="n">
+        <v>63.35</v>
+      </c>
+      <c r="E2162" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="F2162" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2163" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D2163" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="E2163" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F2163" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2164" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="D2164" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E2164" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="F2164" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2165" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="D2165" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="E2165" t="n">
+        <v>49.93</v>
+      </c>
+      <c r="F2165" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2166" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="D2166" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="E2166" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="F2166" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2167" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="D2167" t="n">
+        <v>65.88</v>
+      </c>
+      <c r="E2167" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="F2167" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2168" t="n">
+        <v>63.22</v>
+      </c>
+      <c r="D2168" t="n">
+        <v>63.36</v>
+      </c>
+      <c r="E2168" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="F2168" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2169" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="D2169" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="E2169" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="F2169" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2170" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="D2170" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="E2170" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="F2170" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2171" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D2171" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="E2171" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="F2171" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2172" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="D2172" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="E2172" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="F2172" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2173" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="D2173" t="n">
+        <v>66.13</v>
+      </c>
+      <c r="E2173" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="F2173" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2174" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="D2174" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="E2174" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="F2174" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2175" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="D2175" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E2175" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="F2175" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2176" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="D2176" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="E2176" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="F2176" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2177" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="D2177" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="E2177" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="F2177" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2178" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="D2178" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="E2178" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="F2178" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2179" t="n">
+        <v>65.97</v>
+      </c>
+      <c r="D2179" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="E2179" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="F2179" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2180" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="D2180" t="n">
+        <v>63.18</v>
+      </c>
+      <c r="E2180" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="F2180" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2181" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="D2181" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="E2181" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="F2181" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2182" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="D2182" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="E2182" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F2182" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2183" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="D2183" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="E2183" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="F2183" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2184" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="D2184" t="n">
+        <v>59.54</v>
+      </c>
+      <c r="E2184" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="F2184" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2185" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="D2185" t="n">
+        <v>66.20999999999999</v>
+      </c>
+      <c r="E2185" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="F2185" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2186" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="D2186" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="E2186" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="F2186" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2187" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="D2187" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="E2187" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="F2187" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2188" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="D2188" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E2188" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="F2188" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2189" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="D2189" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="E2189" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="F2189" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2190" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="D2190" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="E2190" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="F2190" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2191" t="n">
+        <v>65.33</v>
+      </c>
+      <c r="D2191" t="n">
+        <v>65.43000000000001</v>
+      </c>
+      <c r="E2191" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="F2191" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2192" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="D2192" t="n">
+        <v>63.09</v>
+      </c>
+      <c r="E2192" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="F2192" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2193" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="D2193" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="E2193" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F2193" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2194" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="D2194" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="E2194" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F2194" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2195" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="D2195" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="E2195" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="F2195" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2196" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="D2196" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="E2196" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="F2196" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2197" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="D2197" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="E2197" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="F2197" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2198" t="n">
+        <v>62.82</v>
+      </c>
+      <c r="D2198" t="n">
+        <v>63.11</v>
+      </c>
+      <c r="E2198" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="F2198" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2199" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="D2199" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="E2199" t="n">
+        <v>56.97</v>
+      </c>
+      <c r="F2199" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2200" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="D2200" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E2200" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2200" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2201" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="D2201" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="E2201" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="F2201" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2202" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="D2202" t="n">
+        <v>60.19</v>
+      </c>
+      <c r="E2202" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="F2202" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2203" t="n">
+        <v>64.83</v>
+      </c>
+      <c r="D2203" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="E2203" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="F2203" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2204" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="D2204" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="E2204" t="n">
+        <v>62.22</v>
+      </c>
+      <c r="F2204" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2205" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="D2205" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="E2205" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="F2205" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2206" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="D2206" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="E2206" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="F2206" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2207" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="D2207" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="E2207" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="F2207" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2208" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="D2208" t="n">
+        <v>59.57</v>
+      </c>
+      <c r="E2208" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="F2208" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2209" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="D2209" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="E2209" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="F2209" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2210" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="D2210" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="E2210" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F2210" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2211" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="D2211" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="E2211" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="F2211" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2212" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="D2212" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="E2212" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="F2212" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2213" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="D2213" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="E2213" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="F2213" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2214" t="n">
+        <v>59.63</v>
+      </c>
+      <c r="D2214" t="n">
+        <v>59.63</v>
+      </c>
+      <c r="E2214" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="F2214" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2215" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="D2215" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="E2215" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="F2215" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2216" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="D2216" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="E2216" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="F2216" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2217" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="D2217" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="E2217" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F2217" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2218" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="D2218" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="E2218" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="F2218" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2219" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="D2219" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="E2219" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="F2219" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2220" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="D2220" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="E2220" t="n">
+        <v>59.43</v>
+      </c>
+      <c r="F2220" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2221" t="n">
+        <v>65.14</v>
+      </c>
+      <c r="D2221" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="E2221" t="n">
+        <v>64.97</v>
+      </c>
+      <c r="F2221" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2222" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="D2222" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="E2222" t="n">
+        <v>62.23</v>
+      </c>
+      <c r="F2222" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2223" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D2223" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="E2223" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="F2223" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2224" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="D2224" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="E2224" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="F2224" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2225" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="D2225" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="E2225" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="F2225" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2226" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="D2226" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="E2226" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="F2226" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2227" t="n">
+        <v>64.88</v>
+      </c>
+      <c r="D2227" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="E2227" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2228" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="D2228" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="E2228" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="F2228" t="n">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2229" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="D2229" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="E2229" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F2229" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2230" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="D2230" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="E2230" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="F2230" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2231" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="D2231" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="E2231" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="F2231" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2232" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="D2232" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2233" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="D2233" t="n">
+        <v>65.26000000000001</v>
+      </c>
+      <c r="E2233" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F2233" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2234" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="D2234" t="n">
+        <v>63.46</v>
+      </c>
+      <c r="E2234" t="n">
+        <v>62.59</v>
+      </c>
+      <c r="F2234" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2235" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="D2235" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="E2235" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="F2235" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2236" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="D2236" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="E2236" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="F2236" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2237" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="D2237" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2238" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D2238" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="E2238" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F2238" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2239" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="D2239" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="E2239" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="F2239" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2240" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="D2240" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2241" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="D2241" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="E2241" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="F2241" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2242" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="D2242" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="E2242" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="F2242" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2243" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="D2243" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2244" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="D2244" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2245" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="D2245" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="E2245" t="n">
+        <v>64.03</v>
+      </c>
+      <c r="F2245" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2246" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="D2246" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>63.01</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2247" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="D2247" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E2247" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="F2247" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2248" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="D2248" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="E2248" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="F2248" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2249" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="D2249" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="E2249" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="F2249" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2250" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="D2250" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="E2250" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="F2250" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2251" t="n">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="D2251" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="E2251" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="F2251" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2252" t="n">
+        <v>62.61</v>
+      </c>
+      <c r="D2252" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="E2252" t="n">
+        <v>62.53</v>
+      </c>
+      <c r="F2252" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2253" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="D2253" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E2253" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="F2253" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2254" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="D2254" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="E2254" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="F2254" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2255" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="D2255" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="E2255" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="F2255" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2256" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="D2256" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="E2256" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="F2256" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2257" t="n">
+        <v>65.23</v>
+      </c>
+      <c r="D2257" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="E2257" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="F2257" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2258" t="n">
+        <v>63.35</v>
+      </c>
+      <c r="D2258" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="E2258" t="n">
+        <v>63.18</v>
+      </c>
+      <c r="F2258" t="n">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2259" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="D2259" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E2259" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="F2259" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2260" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="D2260" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="E2260" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="F2260" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2261" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="D2261" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="E2261" t="n">
+        <v>49.93</v>
+      </c>
+      <c r="F2261" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2262" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="D2262" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="E2262" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="F2262" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2263" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="D2263" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="E2263" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="F2263" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2264" t="n">
+        <v>63.46</v>
+      </c>
+      <c r="D2264" t="n">
+        <v>63.52</v>
+      </c>
+      <c r="E2264" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="F2264" t="n">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2265" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="D2265" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="E2265" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="F2265" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2266" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="D2266" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="E2266" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="F2266" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2267" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D2267" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="E2267" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="F2267" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2268" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="D2268" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="E2268" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="F2268" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2269" t="n">
+        <v>64.81</v>
+      </c>
+      <c r="D2269" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="E2269" t="n">
+        <v>64.61</v>
+      </c>
+      <c r="F2269" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2270" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="D2270" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="E2270" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="F2270" t="n">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2271" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="D2271" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="E2271" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="F2271" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2272" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="D2272" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="E2272" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="F2272" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2273" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="D2273" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="E2273" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="F2273" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2274" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="D2274" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="E2274" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="F2274" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2275" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="D2275" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="E2275" t="n">
+        <v>64.31</v>
+      </c>
+      <c r="F2275" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2276" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="D2276" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="E2276" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F2276" t="n">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2277" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="D2277" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2278" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="D2278" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E2278" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="F2278" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2279" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="D2279" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="F2279" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2280" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2281" t="n">
+        <v>64.84</v>
+      </c>
+      <c r="D2281" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="E2281" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="F2281" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2282" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="D2282" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="E2282" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="F2282" t="n">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2283" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="D2283" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2284" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="D2284" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="E2284" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="F2284" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2285" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2286" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="D2286" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="E2286" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="F2286" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2287" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="D2287" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="E2287" t="n">
+        <v>64.88</v>
+      </c>
+      <c r="F2287" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2288" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="D2288" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="E2288" t="n">
+        <v>63.52</v>
+      </c>
+      <c r="F2288" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2289" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="D2289" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="F2289" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2290" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="D2290" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="E2290" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2290" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2291" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="D2291" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="E2291" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="F2291" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2292" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="D2292" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="E2292" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="F2292" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2293" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2294" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2295" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="D2295" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="F2295" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2296" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="D2296" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="F2296" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2297" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2298" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2299" t="n">
+        <v>64.84</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2300" t="n">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="D2300" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>63.61</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2301" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2302" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="D2302" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2303" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="D2303" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2304" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D2304" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="E2304" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F2304" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2305" t="n">
+        <v>65.13</v>
+      </c>
+      <c r="D2305" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="E2305" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="F2305" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2306" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="D2306" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="E2306" t="n">
+        <v>63.53</v>
+      </c>
+      <c r="F2306" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2307" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2308" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="D2308" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="E2308" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="F2308" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2309" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="D2309" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="E2309" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="F2309" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2310" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="D2310" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="E2310" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="F2310" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2311" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="D2311" t="n">
+        <v>65.42</v>
+      </c>
+      <c r="E2311" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="F2311" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2312" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="D2312" t="n">
+        <v>64.06</v>
+      </c>
+      <c r="E2312" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="F2312" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2313" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="D2313" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="E2313" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="F2313" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2314" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="D2314" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="E2314" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="F2314" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2315" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="D2315" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="E2315" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2316" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="D2316" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="E2316" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="F2316" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2317" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="D2317" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="E2317" t="n">
+        <v>64.53</v>
+      </c>
+      <c r="F2317" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2318" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="D2318" t="n">
+        <v>64.44</v>
+      </c>
+      <c r="E2318" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="F2318" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2319" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="D2319" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="E2319" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="F2319" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2320" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="D2320" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="E2320" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="F2320" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2321" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="D2321" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="E2321" t="n">
+        <v>50.41</v>
+      </c>
+      <c r="F2321" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2322" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="D2322" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="E2322" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="F2322" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2323" t="n">
+        <v>65.43000000000001</v>
+      </c>
+      <c r="D2323" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="E2323" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="F2323" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2324" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="D2324" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="E2324" t="n">
+        <v>63.91</v>
+      </c>
+      <c r="F2324" t="n">
+        <v>64.09999999999999</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2325" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2326" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="D2326" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="E2326" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="F2326" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2327" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="D2327" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="F2327" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2328" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="D2328" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="E2328" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="F2328" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2329" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="E2329" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="F2329" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2330" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>63.53</v>
+      </c>
+      <c r="F2330" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2331" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="D2331" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="E2331" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="F2331" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2332" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="D2332" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="E2332" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="F2332" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2333" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="D2333" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="E2333" t="n">
+        <v>50.59</v>
+      </c>
+      <c r="F2333" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2334" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="D2334" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="E2334" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="F2334" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2335" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="E2335" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="F2335" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2336" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="D2336" t="n">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="E2336" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="F2336" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2337" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="D2337" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="E2337" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="F2337" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2338" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="D2338" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="E2338" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="F2338" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2339" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="D2339" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="E2339" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="F2339" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2340" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="D2340" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="E2340" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="F2340" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2341" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E2341" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="F2341" t="n">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2342" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="F2342" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2343" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>58.58</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="F2343" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2344" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="F2344" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2345" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="F2345" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2346" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="F2346" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2347" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="D2347" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="E2347" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="F2347" t="n">
+        <v>64.59999999999999</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2348" t="n">
+        <v>63.61</v>
+      </c>
+      <c r="D2348" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="E2348" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="F2348" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2349" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2350" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F2350" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2351" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>51.29</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2352" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="F2352" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2353" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="D2353" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="E2353" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="F2353" t="n">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2354" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>64</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F2354" t="n">
+        <v>63.9</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2355" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="F2355" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2356" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="D2356" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E2356" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2356" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2357" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="D2357" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="E2357" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="F2357" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2358" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="D2358" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="E2358" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="F2358" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>去盖臀肉</t>
+        </is>
+      </c>
+      <c r="C2359" t="n">
+        <v>64.84</v>
+      </c>
+      <c r="D2359" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="E2359" t="n">
+        <v>64.67</v>
+      </c>
+      <c r="F2359" t="n">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>大米龙</t>
+        </is>
+      </c>
+      <c r="C2360" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="D2360" t="n">
+        <v>64.03</v>
+      </c>
+      <c r="E2360" t="n">
+        <v>63.54</v>
+      </c>
+      <c r="F2360" t="n">
+        <v>63.9</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C2361" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="D2361" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="E2361" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="F2361" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>牛前后</t>
+        </is>
+      </c>
+      <c r="C2362" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="D2362" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="E2362" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="F2362" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C2363" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="D2363" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="E2363" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F2363" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>牛霖</t>
+        </is>
+      </c>
+      <c r="C2364" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="D2364" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="E2364" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="F2364" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
